--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,11 +733,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.0252348601965</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.0252348601965</v>
+        <v>1.02441050265753</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.0252348601965</v>
+        <v>1.02441050265753</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.03239988471142</v>
+        <v>1.032290678998186</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.027414900915792</v>
+        <v>1.027339819285192</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.027414900915792</v>
+        <v>1.027339819285192</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.027414900915792</v>
+        <v>1.027339819285192</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.027414900915792</v>
+        <v>1.027339819285192</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.028614</v>
+        <v>1.027888</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.028614</v>
+        <v>1.027888</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.028614</v>
+        <v>1.027888</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.029422</v>
+        <v>1.027888</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.028614</v>
+        <v>1.027888</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3261,7 +3261,11 @@
           <t>LFSN1800D4W</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
@@ -3301,7 +3305,11 @@
           <t>LFSN1800D4W</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
@@ -3669,7 +3677,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.016004</v>
+        <v>1.012998</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3713,7 +3721,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.021813</v>
+        <v>1.018941</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3757,11 +3765,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.032555</v>
+        <v>1.041884961211692</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3781,7 +3789,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3794,22 +3802,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.04236373705509</v>
+        <v>1.031229</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3829,12 +3833,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3842,14 +3846,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.04236373705509</v>
+        <v>1.041884961211692</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3873,7 +3881,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3893,11 +3901,11 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.032555</v>
+        <v>1.041884961211692</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J78" t="b">
@@ -3917,27 +3925,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.048077</v>
+        <v>1.031229</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3961,7 +3969,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3981,7 +3989,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.049006</v>
+        <v>1.047128</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4005,7 +4013,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4025,7 +4033,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.048077</v>
+        <v>1.047128</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4049,7 +4057,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4062,22 +4070,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.059268852932506</v>
+        <v>1.047128</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4097,12 +4101,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4110,18 +4114,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.048077</v>
+        <v>1.058331904913108</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4136,36 +4144,36 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -4185,7 +4193,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4229,7 +4237,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4237,7 +4245,11 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
@@ -4269,7 +4281,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4313,7 +4325,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4357,23 +4369,23 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -4401,7 +4413,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4445,7 +4457,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4484,36 +4496,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.08453</v>
+        <v>1.05</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J92" t="b">
@@ -4523,45 +4535,41 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.034712084469143</v>
+        <v>1.08453</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J93" t="b">
@@ -4581,7 +4589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4596,7 +4604,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4605,7 +4613,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4629,7 +4637,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4653,7 +4661,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.034712084469143</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4672,36 +4680,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.0225</v>
+        <v>1.034582917387498</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4725,7 +4733,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4740,7 +4748,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4768,7 +4776,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4778,26 +4786,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.069664153441496</v>
+        <v>1.0225</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4826,17 +4834,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4845,7 +4853,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.069664153441496</v>
+        <v>1.069319289350928</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4874,33 +4882,81 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>1.069319289350928</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H100" t="n">
-        <v>1.069664153441496</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>MATRIZ</t>
-        </is>
-      </c>
-      <c r="J100" t="b">
+      <c r="H101" t="n">
+        <v>1.069319289350928</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.034582917387498</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.034582917387498</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.034582917387498</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.034582917387498</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.034582917387498</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.032290678998186</v>
+        <v>1.03</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.027339819285192</v>
+        <v>1.025</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.027339819285192</v>
+        <v>1.025</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.027339819285192</v>
+        <v>1.025</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.027339819285192</v>
+        <v>1.025</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.027888</v>
+        <v>1.029627</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.027888</v>
+        <v>1.029627</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.027888</v>
+        <v>1.029627</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.027888</v>
+        <v>1.029627</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.027888</v>
+        <v>1.029627</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2412,36 +2412,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.768821448424161</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -2456,36 +2452,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.768821448424161</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -2500,36 +2492,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.768821448424161</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -2544,32 +2532,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.18113603052</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2588,32 +2576,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.18113603052</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2632,32 +2620,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.18113603052</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2686,12 +2674,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2701,11 +2689,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.18113603052</v>
+        <v>1.5822</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -2725,7 +2713,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2769,23 +2757,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2818,26 +2806,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.18113603052</v>
+        <v>1.5822</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -2857,23 +2845,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2906,18 +2894,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2950,18 +2938,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2994,26 +2982,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.18113603052</v>
+        <v>1.5822</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -3033,23 +3021,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -3077,23 +3065,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3116,32 +3104,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.00373305</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3155,12 +3143,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3170,26 +3158,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J62" t="b">
@@ -3199,41 +3187,41 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -3243,41 +3231,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.003</v>
+        <v>0.0035976</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -3297,7 +3285,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3313,7 +3301,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3336,28 +3324,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -3380,32 +3368,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -3428,28 +3412,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3472,28 +3456,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTR2X9</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -3516,28 +3500,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -3560,32 +3548,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+          <t>BRBBDCLTROH4</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3608,36 +3592,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.00373305</v>
+        <v>1.003</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -3657,31 +3641,31 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.012998</v>
+        <v>1.003</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -3701,31 +3685,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.018941</v>
+        <v>1.003</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -3740,36 +3728,36 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.041884961211692</v>
+        <v>0.0035976</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3784,32 +3772,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.031229</v>
+        <v>1.012998</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3828,40 +3816,36 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNBB5</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.041884961211692</v>
+        <v>1.018941</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -3881,12 +3865,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3901,7 +3885,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.041884961211692</v>
+        <v>1.041143607972442</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3925,12 +3909,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3969,31 +3953,35 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.047128</v>
+        <v>1.041143607972442</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -4013,31 +4001,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.047128</v>
+        <v>1.041143607972442</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -4057,27 +4045,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.047128</v>
+        <v>1.031229</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4101,7 +4089,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4114,22 +4102,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.058331904913108</v>
+        <v>1.047128</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4149,12 +4133,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4188,36 +4172,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -4232,32 +4216,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.05</v>
+        <v>1.056944338323399</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4276,36 +4264,36 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -4325,7 +4313,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4369,7 +4357,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4413,23 +4401,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -4457,23 +4445,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -4506,18 +4494,18 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -4540,36 +4528,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.08453</v>
+        <v>1.05</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J93" t="b">
@@ -4579,41 +4567,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.034582917387498</v>
+        <v>1.05</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4627,41 +4611,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.034582917387498</v>
+        <v>1.05</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4675,45 +4655,41 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.034582917387498</v>
+        <v>1.083143</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J96" t="b">
@@ -4728,7 +4704,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4738,12 +4714,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4753,11 +4729,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.0225</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4776,7 +4752,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4786,12 +4762,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4801,11 +4777,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.0225</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4824,36 +4800,36 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.069319289350928</v>
+        <v>1.034380630352743</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4872,36 +4848,36 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.069319289350928</v>
+        <v>1.0225</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4920,43 +4896,187 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1.068820625459148</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1.068820625459148</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>1.069319289350928</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>MATRIZ</t>
-        </is>
-      </c>
-      <c r="J101" t="b">
+      <c r="H104" t="n">
+        <v>1.068820625459148</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J104" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.034380630352743</v>
+        <v>1.034365104608699</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.034380630352743</v>
+        <v>1.034365104608699</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.034380630352743</v>
+        <v>1.034365104608699</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.034380630352743</v>
+        <v>1.034365104608699</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.034380630352743</v>
+        <v>1.034365104608699</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1472,36 +1472,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB8265ICFV</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-12-03 00:00:00</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.02</v>
+        <v>1.029</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -1511,12 +1511,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1526,24 +1526,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB8265ICFW</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>2026-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1.029</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -1553,43 +1555,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB8265ICFX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+          <t>BRRANDC001H9</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>2026-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1.029</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -1599,81 +1599,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB8265ICFY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2026-12-03 00:00:00</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.029627</v>
+        <v>1.029</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO RANDON</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB8265ICFZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRRANDC001H9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2026-12-03 00:00:00</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.029627</v>
+        <v>1.029</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1687,41 +1687,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.029627</v>
+        <v>1.02</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -1736,36 +1736,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRHAPVDBS014</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1.029627</v>
-      </c>
+          <t>2026-07-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -1780,128 +1778,126 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
+          <t>BRHAPVDBS014</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>353017-KLB</t>
+          <t>362409-HAP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>1.029627</v>
-      </c>
+          <t>2026-07-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.0225</v>
+        <v>1.029627</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.0225</v>
+        <v>1.029627</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -1911,45 +1907,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-23 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.0225</v>
+        <v>1.029627</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -1959,41 +1951,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
+          <t>BRKLBNDBS004</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-23 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.0225</v>
+        <v>1.029627</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2003,45 +1995,49 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.035</v>
+        <v>1.029627</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2052,32 +2048,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.035</v>
+        <v>1.0225</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2096,7 +2092,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2106,22 +2102,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO68</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.035</v>
+        <v>1.0225</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2135,37 +2131,41 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>BRBCXPLFIO76</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.035</v>
+        <v>1.0225</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2184,32 +2184,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.035</v>
+        <v>1.0225</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2290,11 +2290,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
@@ -2325,12 +2321,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2338,11 +2334,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>567798-LF0</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
@@ -2373,12 +2365,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2407,33 +2399,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>LF002400KBY</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.768821448424161</v>
+        <v>1.035</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2447,33 +2443,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>LF002400KC0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.768821448424161</v>
+        <v>1.035</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2487,33 +2487,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JERA2026 FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+          <t>LF002400KC0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>567797-LF0</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.768821448424161</v>
+        <v>1.035</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2527,41 +2535,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.035</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -2571,41 +2583,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.035</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -2615,41 +2627,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BRABCBLFN7I2</t>
-        </is>
-      </c>
+          <t>LF00260094N</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2028-03-27 00:00:00</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.045917970641182</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -2659,37 +2667,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI013</t>
-        </is>
-      </c>
+          <t>LF002600MAZ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2028-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.5822</v>
+        <v>1.04859219234482</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2703,41 +2707,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>LF002600MB0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2028-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.18113603052</v>
+        <v>1.04859219234482</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -2747,41 +2747,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>LF002600MB1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2028-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.18113603052</v>
+        <v>1.04859219234482</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -2796,32 +2792,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.5822</v>
+        <v>1.768785114865144</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2840,36 +2832,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI021</t>
-        </is>
-      </c>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.18113603052</v>
+        <v>1.768785114865144</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -2884,36 +2872,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026 FIM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BRBNBRLFI039</t>
-        </is>
-      </c>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2029-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.18113603052</v>
+        <v>1.768785114865144</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -2928,32 +2912,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.18113603052</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2972,7 +2956,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2982,26 +2966,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.5822</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -3016,7 +3000,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3026,22 +3010,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.18113603052</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3070,26 +3054,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.18113603052</v>
+        <v>1.5822</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -3109,23 +3093,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -3153,23 +3137,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3197,31 +3181,31 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.18113603052</v>
+        <v>1.5822</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -3236,32 +3220,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.0035976</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3275,41 +3259,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3319,41 +3303,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3363,37 +3347,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.003</v>
+        <v>1.5822</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3407,41 +3391,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -3451,41 +3435,41 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -3495,45 +3479,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+          <t>BRBNBRLFI0F8</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3543,41 +3523,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -3587,41 +3567,41 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.003</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -3631,41 +3611,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.003</v>
+        <v>0.0035976</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -3685,27 +3665,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -3728,36 +3704,36 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.0035976</v>
+        <v>1.003</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3777,31 +3753,31 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.012998</v>
+        <v>1.003</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3821,31 +3797,31 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.018941</v>
+        <v>1.003</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -3860,7 +3836,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3870,22 +3846,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBBDCLTR2X9</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.041143607972442</v>
+        <v>1.003</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3904,36 +3880,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.031229</v>
+        <v>1.003</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -3948,36 +3928,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBBDCLTROH4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.041143607972442</v>
+        <v>1.003</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3996,32 +3972,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.041143607972442</v>
+        <v>1.003</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4040,36 +4016,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLNN8B3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.031229</v>
+        <v>1.003</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4084,36 +4060,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.047128</v>
+        <v>1.003</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4128,32 +4108,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.047128</v>
+        <v>0.0035976</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4172,32 +4152,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.047128</v>
+        <v>1.012998</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4216,40 +4196,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNBB5</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.056944338323399</v>
+        <v>1.018941</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -4269,31 +4245,31 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.047128</v>
+        <v>1.041087129588219</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -4308,36 +4284,36 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.05</v>
+        <v>1.031229</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -4352,32 +4328,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.05</v>
+        <v>1.041087129588219</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4396,32 +4376,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.05</v>
+        <v>1.041087129588219</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4440,36 +4420,36 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.05</v>
+        <v>1.031229</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -4484,36 +4464,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J92" t="b">
@@ -4528,36 +4508,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J93" t="b">
@@ -4572,36 +4552,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.05</v>
+        <v>1.047128</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J94" t="b">
@@ -4616,32 +4596,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.05</v>
+        <v>1.056841636368675</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4660,32 +4644,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.083143</v>
+        <v>1.047128</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4699,41 +4683,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.034380630352743</v>
+        <v>1.05</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4747,41 +4727,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.034380630352743</v>
+        <v>1.05</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4795,41 +4771,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.034380630352743</v>
+        <v>1.05</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4843,41 +4815,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.0225</v>
+        <v>1.05</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4891,41 +4859,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1.0225</v>
+        <v>1.05</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4939,7 +4903,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4949,31 +4913,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>609712-LFS</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1.068820625459148</v>
+        <v>1.05</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -4987,7 +4947,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4997,31 +4957,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>609711-LFS</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1.068820625459148</v>
+        <v>1.05</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5035,48 +4991,736 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LFSN19009YU</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BANCO SAFRA S.A.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LFSN1900CR5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2029-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>1.083143</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2032-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>1.019347</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2032-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>1.019347</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HORIZONTE FIM</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LFSN2200B4M</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3X5</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2032-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>1.019347</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2032-12-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>1.023139</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2032-12-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>1.023139</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LFSN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CNHCAPITALBM</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HORIZONTE FIM</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LFSN2200GD7</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>BRCNHCLFI3Y3</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2032-12-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>1.023139</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>CDB</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2027-03-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>1.034365104608699</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2027-03-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>1.034365104608699</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>REAL FIM</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2027-03-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>1.034365104608699</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>1.068784274592752</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>1.068784274592752</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H104" t="n">
-        <v>1.068820625459148</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>MATRIZ</t>
-        </is>
-      </c>
-      <c r="J104" t="b">
+      <c r="H119" t="n">
+        <v>1.068784274592752</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J119" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2645,7 +2645,11 @@
           <t>LF00260094N</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIF17</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
@@ -2653,7 +2657,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.045917970641182</v>
+        <v>1.04587439953698</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2685,7 +2689,11 @@
           <t>LF002600MAZ</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
@@ -2693,11 +2701,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.04859219234482</v>
+        <v>1.0585714930908</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -2725,7 +2733,11 @@
           <t>LF002600MB0</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
@@ -2733,11 +2745,11 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.04859219234482</v>
+        <v>1.0585714930908</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -2765,7 +2777,11 @@
           <t>LF002600MB1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BRBMEBLFIFX4</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
@@ -2773,11 +2789,11 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.04859219234482</v>
+        <v>1.0585714930908</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -2805,7 +2821,11 @@
           <t>LFSC19002CD</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
@@ -2813,7 +2833,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.768785114865144</v>
+        <v>1.768712146788241</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2845,7 +2865,11 @@
           <t>LFSC19002CE</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
@@ -2853,7 +2877,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.768785114865144</v>
+        <v>1.768712146788241</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2885,7 +2909,11 @@
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7R2</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
@@ -2893,7 +2921,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.768785114865144</v>
+        <v>1.768712146788241</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4265,7 +4293,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.041087129588219</v>
+        <v>1.040972655686757</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4357,7 +4385,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.041087129588219</v>
+        <v>1.040972655686757</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4401,7 +4429,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.041087129588219</v>
+        <v>1.040972655686757</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4625,7 +4653,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.056841636368675</v>
+        <v>1.056634737207497</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5377,7 +5405,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5425,7 +5453,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5473,7 +5501,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1.034365104608699</v>
+        <v>1.034333585717639</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5617,7 +5645,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1.068784274592752</v>
+        <v>1.068711273214842</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5665,7 +5693,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1.068784274592752</v>
+        <v>1.068711273214842</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5713,7 +5741,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1.068784274592752</v>
+        <v>1.068711273214842</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
